--- a/bulk_question_import_template.xlsx
+++ b/bulk_question_import_template.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Examples'!$A$1:$P$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,7 +43,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,9 +67,11 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,23 +437,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -531,90 +540,16 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>বিজ্ঞান</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>অধ্যায় ৫</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>অধ্যায় ৫ অনুশীলনী</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Class 9 Science Chapter 5</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>উদাহরণ: পানির রাসায়নিক সংকেত কোনটি?</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>H₂O</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CO₂</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O₂</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>H₂</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>পানির একটি অণুতে দুইটি হাইড্রোজেন ও একটি অক্সিজেন থাকে।</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="F2:F12001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O12001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"easy,medium,hard"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -625,138 +560,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Bulk Question Import — নির্দেশনা</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Chapter</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Quiz Title</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Quiz Description</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Quiz Published</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Time Limit</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Correct Answer</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Marks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>আবশ্যক কলাম</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Class, Subject, Chapter, Question, Option A, Option B, Option C, Option D, Correct Answer</t>
+          <t>গণিত</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>সংখ্যা পরিচিতি</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>প্রাথমিক গণিত অনুশীলন</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>শ্রেণি ১ নমুনা Quiz</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>২ + ৩ = কত?</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>৪</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>৫</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>৬</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>৭</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>যোগফল ৫।</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A/B/C/D, 1/2/3/4 অথবা option-এর exact text</t>
+          <t>বিজ্ঞান</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>অধ্যায় ১</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>বিজ্ঞান অনুশীলন</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ষষ্ঠ শ্রেণির নমুনা Quiz</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>সৌরজগতের কেন্দ্র কোনটি?</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>চাঁদ</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>সূর্য</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>পৃথিবী</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>মঙ্গল</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>সূর্য কেন্দ্রীয় নক্ষত্র।</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>easy / medium / hard; blank হলে medium</t>
+          <t>পদার্থবিজ্ঞান</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>অধ্যায় ১</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>উচ্চ মাধ্যমিক নমুনা</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>শ্রেণি ১২ নমুনা Quiz</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>বেগের SI একক কী?</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>বেগের SI একক মিটার/সেকেন্ড।</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bulk Question Import — v5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>কোন sheet upload করবেন?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Questions sheet। Examples sheet শুধু format বোঝার জন্য।</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>আবশ্যক কলাম</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Class, Subject, Chapter, Question, Option A, Option B, Option C, Option D, Correct Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1–12; যেমন 1, 6, 12, Class 9, Grade 10, শ্রেণি ১২।</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t>Correct Answer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>পূর্ণসংখ্যা; blank হলে 1</t>
+          <t>A/B/C/D, 1/2/3/4 অথবা option-এর exact text।</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quiz Title</t>
+          <t>Difficulty</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>দিলে import-এর সময় Quiz তৈরি/পুনঃব্যবহার হবে; blank রাখলে শুধু Question Bank-এ প্রশ্ন যাবে</t>
+          <t>easy / medium / hard; blank হলে medium।</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quiz Published</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yes/No, True/False বা 1/0</t>
+          <t>পূর্ণসংখ্যা; blank হলে 1।</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Time Limit</t>
+          <t>Quiz Title</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>মিনিটে; 0 মানে no limit</t>
+          <t>দিলে সংশ্লিষ্ট Class + Subject + Chapter-এর Quiz তৈরি/পুনঃব্যবহার হবে।</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Quiz Published</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>একই Class + Chapter + Question আগে থাকলে নতুন duplicate question হবে না; existing question reuse হবে</t>
+          <t>Yes/No, True/False বা 1/0।</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>Time Limit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CSV হলে UTF-8 with BOM ব্যবহার করুন; .xlsx বেশি সুবিধাজনক</t>
+          <t>মিনিটে; 0 মানে no limit।</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>উদাহরণ</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Class 9 + বিজ্ঞান + অধ্যায় ৫-এর ৩০টি প্রশ্ন হলে ৩০টি data row দিন।</t>
+          <t>প্রতি Class-এ সর্বোচ্চ 1000 প্রশ্ন; 1–12 Class মিলিয়ে configured capacity 12000।</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Preview</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Preview data database-এ রাখা হয়; 60 মিনিটের মধ্যে Confirm করা যায়, server restart হলেও।</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UTF-8 with BOM ব্যবহার করুন।</t>
         </is>
       </c>
     </row>

--- a/bulk_question_import_template.xlsx
+++ b/bulk_question_import_template.xlsx
@@ -543,10 +543,10 @@
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F12001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F120001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O12001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O120001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
   </dataValidations>
@@ -931,7 +931,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Bulk Question Import — v5.0</t>
+          <t>Bulk Question Import — v5.2</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>প্রতি Class-এ সর্বোচ্চ 1000 প্রশ্ন; 1–12 Class মিলিয়ে configured capacity 12000।</t>
+          <t>প্রতি Class-এ সর্বোচ্চ 10000 প্রশ্ন; 1–12 Class মিলিয়ে configured capacity 120000।</t>
         </is>
       </c>
     </row>

--- a/bulk_question_import_template.xlsx
+++ b/bulk_question_import_template.xlsx
@@ -543,10 +543,10 @@
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F120001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F12001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O120001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O12001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
   </dataValidations>
@@ -931,7 +931,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Bulk Question Import — v5.2</t>
+          <t>Bulk Question Import — v5.0</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>প্রতি Class-এ সর্বোচ্চ 10000 প্রশ্ন; 1–12 Class মিলিয়ে configured capacity 120000।</t>
+          <t>প্রতি Class-এ সর্বোচ্চ 1000 প্রশ্ন; 1–12 Class মিলিয়ে configured capacity 12000।</t>
         </is>
       </c>
     </row>
